--- a/output/pdf_financials_xlsx/KNOX.xlsx
+++ b/output/pdf_financials_xlsx/KNOX.xlsx
@@ -5483,46 +5483,46 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.050708</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.052219</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.118848</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.133967</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.081888</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.303734</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.391909</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.509381</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.5207889999999999</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.539262</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.6273609999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.864491</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.864491</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.864491</v>
       </c>
     </row>
     <row r="93">
@@ -8888,7 +8888,11 @@
           <t>Reserve 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10235,7 +10239,11 @@
           <t>Reserve 6</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11101,7 +11109,11 @@
           <t>Reserve 7</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -13664,7 +13676,11 @@
           <t>Reserve 5</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -16985,7 +17001,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -17608,7 +17628,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -18599,7 +18623,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -19580,7 +19608,11 @@
           <t>Share-based payment reserve 6</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KNOX.xlsx
+++ b/output/pdf_financials_xlsx/KNOX.xlsx
@@ -1006,16 +1006,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001687</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001638</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000595</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-7.9e-05</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.251351</v>
+        <v>-0.250756</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.107449</v>
+        <v>-0.10737</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.103839</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.251351</v>
+        <v>-0.250756</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.107449</v>
+        <v>-0.10737</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.103839</v>
@@ -2304,49 +2304,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.173491</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002158</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003489</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.965357</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.26068</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.128339</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.293721</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.475968</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.046766</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000927</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.03827</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.019548</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.108756</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.032325</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.139946</v>
       </c>
     </row>
     <row r="35">
@@ -2408,49 +2408,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.173491</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.257</v>
+        <v>0.259158</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.111</v>
+        <v>0.114489</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.011</v>
+        <v>0.976357</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.26068</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.128339</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.293721</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.475968</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.046766</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000927</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.03827</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.019548</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.108756</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.032325</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.139946</v>
       </c>
     </row>
     <row r="37">
@@ -3038,43 +3038,43 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.006886</v>
+        <v>0.003397</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.169221</v>
+        <v>0.203864</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.263713</v>
+        <v>0.003033</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.144731</v>
+        <v>0.016392</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.331675</v>
+        <v>0.037954</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.762406</v>
+        <v>0.286438</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.05357</v>
+        <v>0.006804</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.008248999999999999</v>
+        <v>0.007322</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.049226</v>
+        <v>0.010956</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.021448</v>
+        <v>0.0019</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.125284</v>
+        <v>0.016528</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.139946</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -27484,7 +27484,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -33158,7 +33158,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -34056,7 +34056,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -35658,7 +35658,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">

--- a/output/pdf_financials_xlsx/KNOX.xlsx
+++ b/output/pdf_financials_xlsx/KNOX.xlsx
@@ -765,13 +765,13 @@
         <v>0.125225</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.498619</v>
+        <v>0.504619</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.277175</v>
+        <v>0.289175</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.168943</v>
+        <v>0.193943</v>
       </c>
     </row>
     <row r="8">
@@ -927,13 +927,13 @@
         <v>0.624726</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.238684</v>
+        <v>1.244684</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.296135</v>
+        <v>0.308135</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.279943</v>
+        <v>0.304943</v>
       </c>
     </row>
     <row r="11">
@@ -3980,7 +3980,7 @@
         <v>0.490696</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.283485</v>
       </c>
     </row>
     <row r="65">
@@ -4121,22 +4121,22 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.000583</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.023582</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.231834</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.1205</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.13658</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.134579</v>
       </c>
     </row>
     <row r="68">
@@ -4173,16 +4173,16 @@
         <v>0.07868600000000001</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.839916</v>
+        <v>0.840499</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>1.072031</v>
+        <v>1.095613</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>1.029876</v>
+        <v>1.26171</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.452509</v>
+        <v>0.573009</v>
       </c>
       <c r="O68" s="3" t="n">
         <v>0.501201</v>
@@ -4537,10 +4537,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.179035</v>
+        <v>0.178452</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.343917</v>
+        <v>0.320335</v>
       </c>
       <c r="M75" s="3" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S324"/>
+  <dimension ref="A1:S325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22024,7 +22024,11 @@
           <t>Proceeds of private placement</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -22263,10 +22267,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F164" s="5" t="n">
+        <v>0.173491</v>
       </c>
       <c r="G164" s="5" t="n">
         <v>0.002158</v>
@@ -24185,10 +24187,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F186" s="5" t="n">
+        <v>-0.257</v>
       </c>
       <c r="G186" s="5" t="n">
         <v>0.146</v>
@@ -24264,7 +24264,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -25797,7 +25801,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E204" s="5" t="n">
         <v>0.2</v>
       </c>
@@ -26062,10 +26070,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F207" s="5" t="n">
+        <v>0.002158</v>
       </c>
       <c r="G207" s="5" t="n">
         <v>0.003489</v>
@@ -26489,7 +26495,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -26831,25 +26841,29 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>For the period from</t>
+          <t>Due to related party                                         509                    −</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" s="5" t="n">
-        <v>0.002011</v>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F216" s="5" t="n">
-        <v>9e-06</v>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.101534</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>-0.144669</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -26920,20 +26934,24 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>For the period from</t>
+          <t>Supplementary cash flow information</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>May 31, 2012 May</t>
+          <t>Cash paid for interest $</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
-      <c r="E217" s="5" t="n">
-        <v>0.002011</v>
-      </c>
-      <c r="F217" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -27009,26 +27027,24 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplementary cash flow information</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Cash paid for income taxes $</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F218" s="5" t="n">
-        <v>0.173491</v>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -27104,24 +27120,20 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>For the period from</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" s="5" t="n">
-        <v>0.173491</v>
+        <v>0.002011</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>0.002158</v>
+        <v>9e-06</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -27197,24 +27209,20 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information</t>
+          <t>For the period from</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cash paid for interest $</t>
+          <t>May 31, 2012 May</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E220" s="5" t="n">
+        <v>0.002011</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -27290,24 +27298,26 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cash paid for income taxes $</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F221" s="5" t="n">
+        <v>0.173491</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -27378,36 +27388,34 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G222" s="5" t="n">
-        <v>0.0224</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>0.173491</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>0.002158</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -27459,11 +27467,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R222" s="5" t="n">
-        <v>0.01396</v>
-      </c>
-      <c r="S222" s="5" t="n">
-        <v>0.111</v>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -27479,12 +27491,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -27497,10 +27509,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G223" s="5" t="n">
+        <v>0.0224</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -27542,17 +27552,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P223" s="5" t="n">
-        <v>0.007597</v>
-      </c>
-      <c r="Q223" s="5" t="n">
-        <v>0.011596</v>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R223" s="5" t="n">
-        <v>0.020667</v>
+        <v>0.01396</v>
       </c>
       <c r="S223" s="5" t="n">
-        <v>0.01877</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="224">
@@ -27568,12 +27582,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -27606,36 +27620,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K224" s="5" t="n">
-        <v>0.105977</v>
-      </c>
-      <c r="L224" s="5" t="n">
-        <v>0.065662</v>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N224" s="5" t="n">
-        <v>0.055359</v>
-      </c>
-      <c r="O224" s="5" t="n">
-        <v>0.011229</v>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P224" s="5" t="n">
-        <v>0.007336</v>
+        <v>0.007597</v>
       </c>
       <c r="Q224" s="5" t="n">
-        <v>0.265</v>
+        <v>0.011596</v>
       </c>
       <c r="R224" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.020667</v>
+      </c>
+      <c r="S224" s="5" t="n">
+        <v>0.01877</v>
       </c>
     </row>
     <row r="225">
@@ -27651,12 +27671,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Advertising and investor relations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -27689,41 +27709,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K225" s="5" t="n">
+        <v>0.105977</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>0.065662</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N225" s="5" t="n">
+        <v>0.055359</v>
+      </c>
+      <c r="O225" s="5" t="n">
+        <v>0.011229</v>
+      </c>
+      <c r="P225" s="5" t="n">
+        <v>0.007336</v>
       </c>
       <c r="Q225" s="5" t="n">
-        <v>0.233</v>
+        <v>0.265</v>
       </c>
       <c r="R225" s="5" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -27744,7 +27754,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Office and administration</t>
+          <t>Advertising and investor relations</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27797,23 +27807,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N226" s="5" t="n">
-        <v>0.06057</v>
-      </c>
-      <c r="O226" s="5" t="n">
-        <v>0.038711</v>
-      </c>
-      <c r="P226" s="5" t="n">
-        <v>0.061557</v>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q226" s="5" t="n">
-        <v>0.094675</v>
+        <v>0.233</v>
       </c>
       <c r="R226" s="5" t="n">
-        <v>0.125641</v>
-      </c>
-      <c r="S226" s="5" t="n">
-        <v>0.063517</v>
+        <v>0.013</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -27829,37 +27847,53 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and administration</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E227" s="5" t="n">
-        <v>0.025482</v>
-      </c>
-      <c r="F227" s="5" t="n">
-        <v>0.035687</v>
-      </c>
-      <c r="G227" s="5" t="n">
-        <v>0.060294</v>
-      </c>
-      <c r="H227" s="5" t="n">
-        <v>0.138562</v>
-      </c>
-      <c r="I227" s="5" t="n">
-        <v>0.053465</v>
-      </c>
-      <c r="J227" s="5" t="n">
-        <v>0.041963</v>
-      </c>
-      <c r="K227" s="5" t="n">
-        <v>0.027516</v>
-      </c>
-      <c r="L227" s="5" t="n">
-        <v>0.028317</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -27867,22 +27901,22 @@
         </is>
       </c>
       <c r="N227" s="5" t="n">
-        <v>0.09365</v>
+        <v>0.06057</v>
       </c>
       <c r="O227" s="5" t="n">
-        <v>0.137974</v>
+        <v>0.038711</v>
       </c>
       <c r="P227" s="5" t="n">
-        <v>0.08547100000000001</v>
+        <v>0.061557</v>
       </c>
       <c r="Q227" s="5" t="n">
-        <v>0.193089</v>
+        <v>0.094675</v>
       </c>
       <c r="R227" s="5" t="n">
-        <v>0.0289</v>
+        <v>0.125641</v>
       </c>
       <c r="S227" s="5" t="n">
-        <v>0.012171</v>
+        <v>0.063517</v>
       </c>
     </row>
     <row r="228">
@@ -27898,82 +27932,60 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Project investigation</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="n">
+        <v>0.025482</v>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>0.035687</v>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>0.060294</v>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>0.138562</v>
+      </c>
+      <c r="I228" s="5" t="n">
+        <v>0.053465</v>
+      </c>
+      <c r="J228" s="5" t="n">
+        <v>0.041963</v>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>0.027516</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>0.028317</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N228" s="5" t="n">
+        <v>0.09365</v>
+      </c>
+      <c r="O228" s="5" t="n">
+        <v>0.137974</v>
+      </c>
+      <c r="P228" s="5" t="n">
+        <v>0.08547100000000001</v>
+      </c>
+      <c r="Q228" s="5" t="n">
+        <v>0.193089</v>
+      </c>
+      <c r="R228" s="5" t="n">
+        <v>0.0289</v>
       </c>
       <c r="S228" s="5" t="n">
-        <v>0.01689</v>
+        <v>0.012171</v>
       </c>
     </row>
     <row r="229">
@@ -27989,14 +28001,10 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Management fees 8</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Project investigation</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -28042,8 +28050,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N229" s="5" t="n">
-        <v>0.022</v>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -28055,14 +28065,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q229" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="R229" s="5" t="n">
-        <v>0.12</v>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S229" s="5" t="n">
-        <v>0.09</v>
+        <v>0.01689</v>
       </c>
     </row>
     <row r="230">
@@ -28078,10 +28092,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Directors fees 8</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Management fees 8</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -28127,10 +28145,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N230" s="5" t="n">
+        <v>0.022</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -28143,13 +28159,13 @@
         </is>
       </c>
       <c r="Q230" s="5" t="n">
-        <v>0.006</v>
+        <v>0.08</v>
       </c>
       <c r="R230" s="5" t="n">
-        <v>0.012</v>
+        <v>0.12</v>
       </c>
       <c r="S230" s="5" t="n">
-        <v>0.025</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="231">
@@ -28165,7 +28181,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
+          <t>Directors fees 8</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -28173,52 +28189,74 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E231" s="5" t="n">
-        <v>0.005947</v>
-      </c>
-      <c r="F231" s="5" t="n">
-        <v>0.014669</v>
-      </c>
-      <c r="G231" s="5" t="n">
-        <v>0.019084</v>
-      </c>
-      <c r="H231" s="5" t="n">
-        <v>0.012581</v>
-      </c>
-      <c r="I231" s="5" t="n">
-        <v>0.007312</v>
-      </c>
-      <c r="J231" s="5" t="n">
-        <v>0.009091999999999999</v>
-      </c>
-      <c r="K231" s="5" t="n">
-        <v>0.009065</v>
-      </c>
-      <c r="L231" s="5" t="n">
-        <v>0.008618000000000001</v>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N231" s="5" t="n">
-        <v>0.035905</v>
-      </c>
-      <c r="O231" s="5" t="n">
-        <v>0.029705</v>
-      </c>
-      <c r="P231" s="5" t="n">
-        <v>0.063668</v>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q231" s="5" t="n">
-        <v>0.047064</v>
+        <v>0.006</v>
       </c>
       <c r="R231" s="5" t="n">
-        <v>0.018534</v>
+        <v>0.012</v>
       </c>
       <c r="S231" s="5" t="n">
-        <v>0.015426</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="232">
@@ -28234,78 +28272,60 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Travel and related</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Regulatory fees</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="n">
+        <v>0.005947</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>0.014669</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>0.019084</v>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>0.012581</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>0.007312</v>
+      </c>
+      <c r="J232" s="5" t="n">
+        <v>0.009091999999999999</v>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>0.009065</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>0.008618000000000001</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N232" s="5" t="n">
+        <v>0.035905</v>
+      </c>
+      <c r="O232" s="5" t="n">
+        <v>0.029705</v>
+      </c>
+      <c r="P232" s="5" t="n">
+        <v>0.063668</v>
       </c>
       <c r="Q232" s="5" t="n">
-        <v>0.030555</v>
+        <v>0.047064</v>
       </c>
       <c r="R232" s="5" t="n">
-        <v>0.016206</v>
+        <v>0.018534</v>
       </c>
       <c r="S232" s="5" t="n">
-        <v>0.013437</v>
+        <v>0.015426</v>
       </c>
     </row>
     <row r="233">
@@ -28321,14 +28341,10 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Travel and related</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -28374,23 +28390,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N233" s="5" t="n">
-        <v>-0.419467</v>
-      </c>
-      <c r="O233" s="5" t="n">
-        <v>-0.311684</v>
-      </c>
-      <c r="P233" s="5" t="n">
-        <v>-0.872086</v>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q233" s="5" t="n">
-        <v>-1.611686</v>
+        <v>0.030555</v>
       </c>
       <c r="R233" s="5" t="n">
-        <v>-0.373908</v>
+        <v>0.016206</v>
       </c>
       <c r="S233" s="5" t="n">
-        <v>-0.366211</v>
+        <v>0.013437</v>
       </c>
     </row>
     <row r="234">
@@ -28406,10 +28428,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Gain on forgiveness of accounts payable</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -28455,33 +28481,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N234" s="5" t="n">
+        <v>-0.419467</v>
+      </c>
+      <c r="O234" s="5" t="n">
+        <v>-0.311684</v>
+      </c>
+      <c r="P234" s="5" t="n">
+        <v>-0.872086</v>
+      </c>
+      <c r="Q234" s="5" t="n">
+        <v>-1.611686</v>
+      </c>
+      <c r="R234" s="5" t="n">
+        <v>-0.373908</v>
       </c>
       <c r="S234" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.366211</v>
       </c>
     </row>
     <row r="235">
@@ -28497,7 +28513,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Loss on sale of exploration and evaluation assets 4</t>
+          <t>Gain on forgiveness of accounts payable</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -28561,16 +28577,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q235" s="5" t="n">
-        <v>-0.142667</v>
-      </c>
-      <c r="R235" s="5" t="n">
-        <v>-0.840238</v>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S235" s="5" t="n">
+        <v>-0.0325</v>
       </c>
     </row>
     <row r="236">
@@ -28586,14 +28604,10 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on sale of exploration and evaluation assets 4</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -28654,16 +28668,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q236" s="5" t="n">
+        <v>-0.142667</v>
       </c>
       <c r="R236" s="5" t="n">
-        <v>-1.214146</v>
-      </c>
-      <c r="S236" s="5" t="n">
-        <v>-0.333711</v>
+        <v>-0.840238</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -28679,12 +28693,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Loss per common share basic and diluted</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -28753,10 +28767,10 @@
         </is>
       </c>
       <c r="R237" s="5" t="n">
-        <v>-2.6e-07</v>
+        <v>-1.214146</v>
       </c>
       <c r="S237" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-0.333711</v>
       </c>
     </row>
     <row r="238">
@@ -28767,17 +28781,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per common share basic and diluted</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -28825,11 +28839,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N238" s="5" t="n">
-        <v>54.686587</v>
-      </c>
-      <c r="O238" s="5" t="n">
-        <v>54.75508</v>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
@@ -28842,10 +28860,10 @@
         </is>
       </c>
       <c r="R238" s="5" t="n">
-        <v>4.74123</v>
+        <v>-2.6e-07</v>
       </c>
       <c r="S238" s="5" t="n">
-        <v>5.304792</v>
+        <v>-5.999999999999999e-08</v>
       </c>
     </row>
     <row r="239">
@@ -28856,17 +28874,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Consulting 7</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -28914,27 +28932,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N239" s="5" t="n">
+        <v>54.686587</v>
       </c>
       <c r="O239" s="5" t="n">
-        <v>0.030139</v>
-      </c>
-      <c r="P239" s="5" t="n">
-        <v>0.492165</v>
-      </c>
-      <c r="Q239" s="5" t="n">
-        <v>0.475065</v>
+        <v>54.75508</v>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R239" s="5" t="n">
-        <v>0.01396</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.74123</v>
+      </c>
+      <c r="S239" s="5" t="n">
+        <v>5.304792</v>
       </c>
     </row>
     <row r="240">
@@ -28950,10 +28968,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Directors fees 7</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>Consulting 7</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -29004,21 +29026,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O240" s="5" t="n">
+        <v>0.030139</v>
+      </c>
+      <c r="P240" s="5" t="n">
+        <v>0.492165</v>
       </c>
       <c r="Q240" s="5" t="n">
-        <v>0.006</v>
+        <v>0.475065</v>
       </c>
       <c r="R240" s="5" t="n">
-        <v>0.012</v>
+        <v>0.01396</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -29039,7 +29057,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Management fees 7</t>
+          <t>Directors fees 7</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29108,10 +29126,10 @@
         </is>
       </c>
       <c r="Q241" s="5" t="n">
-        <v>0.08</v>
+        <v>0.006</v>
       </c>
       <c r="R241" s="5" t="n">
-        <v>0.12</v>
+        <v>0.012</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -29132,10 +29150,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Stock-based compensation 6,7</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>Management fees 7</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -29186,19 +29208,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O242" s="5" t="n">
-        <v>0.018473</v>
-      </c>
-      <c r="P242" s="5" t="n">
-        <v>0.088099</v>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q242" s="5" t="n">
-        <v>0.131762</v>
-      </c>
-      <c r="R242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08</v>
+      </c>
+      <c r="R242" s="5" t="n">
+        <v>0.12</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -29219,14 +29243,10 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Shareholder communications</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Stock-based compensation 6,7</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -29277,18 +29297,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O243" s="5" t="n">
+        <v>0.018473</v>
+      </c>
+      <c r="P243" s="5" t="n">
+        <v>0.088099</v>
       </c>
       <c r="Q243" s="5" t="n">
-        <v>0.04388</v>
+        <v>0.131762</v>
       </c>
       <c r="R243" t="inlineStr">
         <is>
@@ -29314,12 +29330,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Shareholder communications</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -29377,11 +29393,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P244" s="5" t="n">
-        <v>-0.000782</v>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q244" s="5" t="n">
-        <v>-0.000103</v>
+        <v>0.04388</v>
       </c>
       <c r="R244" t="inlineStr">
         <is>
@@ -29407,10 +29425,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium liability</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -29466,13 +29488,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P245" s="5" t="n">
+        <v>-0.000782</v>
       </c>
       <c r="Q245" s="5" t="n">
-        <v>0.022828</v>
+        <v>-0.000103</v>
       </c>
       <c r="R245" t="inlineStr">
         <is>
@@ -29498,7 +29518,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Gain on debt settlement</t>
+          <t>Amortization of flow-through premium liability</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -29563,7 +29583,7 @@
         </is>
       </c>
       <c r="Q246" s="5" t="n">
-        <v>0.085395</v>
+        <v>0.022828</v>
       </c>
       <c r="R246" t="inlineStr">
         <is>
@@ -29589,7 +29609,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Write-off of deposit</t>
+          <t>Gain on debt settlement</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -29654,7 +29674,7 @@
         </is>
       </c>
       <c r="Q247" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.085395</v>
       </c>
       <c r="R247" t="inlineStr">
         <is>
@@ -29680,14 +29700,10 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-off of deposit</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -29733,20 +29749,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N248" s="5" t="n">
-        <v>-1.17211</v>
-      </c>
-      <c r="O248" s="5" t="n">
-        <v>-0.310319</v>
-      </c>
-      <c r="P248" s="5" t="n">
-        <v>-0.489993</v>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q248" s="5" t="n">
-        <v>-1.661733</v>
-      </c>
-      <c r="R248" s="5" t="n">
-        <v>-1.214146</v>
+        <v>-0.0155</v>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -29762,17 +29786,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Loss per common share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Net and comprehensive loss</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -29821,19 +29845,19 @@
         </is>
       </c>
       <c r="N249" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-1.17211</v>
       </c>
       <c r="O249" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.310319</v>
       </c>
       <c r="P249" s="5" t="n">
-        <v>-5.8e-07</v>
+        <v>-0.489993</v>
       </c>
       <c r="Q249" s="5" t="n">
-        <v>-5.3e-07</v>
+        <v>-1.661733</v>
       </c>
       <c r="R249" s="5" t="n">
-        <v>-2.6e-07</v>
+        <v>-1.214146</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -29849,15 +29873,19 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per common share</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding total</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -29903,26 +29931,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N250" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="O250" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="P250" s="5" t="n">
+        <v>-5.8e-07</v>
       </c>
       <c r="Q250" s="5" t="n">
-        <v>3.135822</v>
+        <v>-5.3e-07</v>
       </c>
       <c r="R250" s="5" t="n">
-        <v>4.74123</v>
+        <v>-2.6e-07</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -29938,19 +29960,15 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Consulting 8</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding total</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -29996,22 +30014,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N251" s="5" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O251" s="5" t="n">
-        <v>0.030139</v>
-      </c>
-      <c r="P251" s="5" t="n">
-        <v>0.492165</v>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q251" s="5" t="n">
-        <v>0.475065</v>
-      </c>
-      <c r="R251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.135822</v>
+      </c>
+      <c r="R251" s="5" t="n">
+        <v>4.74123</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -30032,10 +30054,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Exploration expenses</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>Consulting 8</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -30081,23 +30107,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N252" s="5" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O252" s="5" t="n">
+        <v>0.030139</v>
       </c>
       <c r="P252" s="5" t="n">
-        <v>0.00088</v>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.492165</v>
+      </c>
+      <c r="Q252" s="5" t="n">
+        <v>0.475065</v>
       </c>
       <c r="R252" t="inlineStr">
         <is>
@@ -30123,7 +30143,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Wages and salaries 8</t>
+          <t>Exploration expenses</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -30172,14 +30192,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N253" s="5" t="n">
-        <v>0.105575</v>
-      </c>
-      <c r="O253" s="5" t="n">
-        <v>0.045453</v>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P253" s="5" t="n">
-        <v>0.065313</v>
+        <v>0.00088</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -30210,7 +30234,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Stock-based compensation 7,8</t>
+          <t>Wages and salaries 8</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -30259,21 +30283,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N254" s="5" t="n">
+        <v>0.105575</v>
+      </c>
+      <c r="O254" s="5" t="n">
+        <v>0.045453</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.088099</v>
-      </c>
-      <c r="Q254" s="5" t="n">
-        <v>0.131762</v>
+        <v>0.065313</v>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
@@ -30299,7 +30321,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Gain on forgiveness of accounts payable 5</t>
+          <t>Stock-based compensation 7,8</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -30359,12 +30381,10 @@
         </is>
       </c>
       <c r="P255" s="5" t="n">
-        <v>0.6446190000000001</v>
-      </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.088099</v>
+      </c>
+      <c r="Q255" s="5" t="n">
+        <v>0.131762</v>
       </c>
       <c r="R255" t="inlineStr">
         <is>
@@ -30390,7 +30410,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Loss on assignment of reclamation bond to JV partner</t>
+          <t>Gain on forgiveness of accounts payable 5</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -30450,7 +30470,7 @@
         </is>
       </c>
       <c r="P256" s="5" t="n">
-        <v>-0.06687700000000001</v>
+        <v>0.6446190000000001</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -30481,7 +30501,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets 4</t>
+          <t>Loss on assignment of reclamation bond to JV partner</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -30530,8 +30550,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N257" s="5" t="n">
-        <v>-0.752643</v>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -30539,7 +30561,7 @@
         </is>
       </c>
       <c r="P257" s="5" t="n">
-        <v>-0.194867</v>
+        <v>-0.06687700000000001</v>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
@@ -30570,7 +30592,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium liability 6</t>
+          <t>Write-off of exploration and evaluation assets 4</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -30619,23 +30641,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N258" s="5" t="n">
+        <v>-0.752643</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q258" s="5" t="n">
-        <v>0.022828</v>
+      <c r="P258" s="5" t="n">
+        <v>-0.194867</v>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
@@ -30656,12 +30676,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding1</t>
+          <t>Amortization of flow-through premium liability 6</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -30715,14 +30735,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O259" s="5" t="n">
-        <v>5.475508</v>
-      </c>
-      <c r="P259" s="5" t="n">
-        <v>0.838234</v>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q259" s="5" t="n">
-        <v>3.135822</v>
+        <v>0.022828</v>
       </c>
       <c r="R259" t="inlineStr">
         <is>
@@ -30748,7 +30772,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1 Post 10:1 share consolidation completed subsequent to May</t>
+          <t>Weighted average number of common shares outstanding1</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -30802,16 +30826,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O260" s="5" t="n">
+        <v>5.475508</v>
       </c>
       <c r="P260" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.838234</v>
       </c>
       <c r="Q260" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>3.135822</v>
       </c>
       <c r="R260" t="inlineStr">
         <is>
@@ -30832,12 +30854,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Wages and salaries 7</t>
+          <t>1 Post 10:1 share consolidation completed subsequent to May</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -30891,16 +30913,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O261" s="5" t="n">
-        <v>0.045453</v>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P261" s="5" t="n">
-        <v>0.065313</v>
-      </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="Q261" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="R261" t="inlineStr">
         <is>
@@ -30926,14 +30948,10 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Wages and salaries 7</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -30985,10 +31003,10 @@
         </is>
       </c>
       <c r="O262" s="5" t="n">
-        <v>0.001365</v>
+        <v>0.045453</v>
       </c>
       <c r="P262" s="5" t="n">
-        <v>-0.000782</v>
+        <v>0.065313</v>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
@@ -31019,10 +31037,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Loss on assignment of reclamation bond to JV Partner 4</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -31073,13 +31095,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O263" s="5" t="n">
+        <v>0.001365</v>
       </c>
       <c r="P263" s="5" t="n">
-        <v>-0.06687700000000001</v>
+        <v>-0.000782</v>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
@@ -31110,7 +31130,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Stock-based compensation 6,8</t>
+          <t>Loss on assignment of reclamation bond to JV Partner 4</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -31159,16 +31179,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N264" s="5" t="n">
-        <v>0.011408</v>
-      </c>
-      <c r="O264" s="5" t="n">
-        <v>0.018473</v>
-      </c>
-      <c r="P264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P264" s="5" t="n">
+        <v>-0.06687700000000001</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -31199,14 +31221,10 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Stock-based compensation 6,8</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -31252,13 +31270,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N265" s="5" t="n">
+        <v>0.011408</v>
       </c>
       <c r="O265" s="5" t="n">
-        <v>0.001365</v>
+        <v>0.018473</v>
       </c>
       <c r="P265" t="inlineStr">
         <is>
@@ -31294,12 +31310,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Consulting $</t>
+          <t>Foreign exchange gain</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -31332,11 +31348,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K266" s="5" t="n">
-        <v>0.081362</v>
-      </c>
-      <c r="L266" s="5" t="n">
-        <v>0.025389</v>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
@@ -31348,10 +31368,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O266" s="5" t="n">
+        <v>0.001365</v>
       </c>
       <c r="P266" t="inlineStr">
         <is>
@@ -31387,12 +31405,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Office and administration 8</t>
+          <t>Consulting $</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -31415,17 +31433,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I267" s="5" t="n">
-        <v>0.049035</v>
-      </c>
-      <c r="J267" s="5" t="n">
-        <v>0.0384</v>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>0.044971</v>
+        <v>0.081362</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>0.040917</v>
+        <v>0.025389</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
@@ -31476,7 +31498,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Rent 8</t>
+          <t>Office and administration 8</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -31505,16 +31527,16 @@
         </is>
       </c>
       <c r="I268" s="5" t="n">
-        <v>0.012</v>
+        <v>0.049035</v>
       </c>
       <c r="J268" s="5" t="n">
-        <v>0.012</v>
+        <v>0.0384</v>
       </c>
       <c r="K268" s="5" t="n">
-        <v>0.012</v>
+        <v>0.044971</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.040917</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
@@ -31565,10 +31587,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Share-based compensation 7(e)</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
+          <t>Rent 8</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -31589,21 +31615,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I269" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="J269" s="5" t="n">
+        <v>0.012</v>
       </c>
       <c r="K269" s="5" t="n">
-        <v>0.191871</v>
+        <v>0.012</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>0.041548</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
@@ -31654,39 +31676,45 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation 7(e)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F270" s="5" t="n">
-        <v>0.006381</v>
-      </c>
-      <c r="G270" s="5" t="n">
-        <v>0.008324</v>
-      </c>
-      <c r="H270" s="5" t="n">
-        <v>0.011285</v>
-      </c>
-      <c r="I270" s="5" t="n">
-        <v>0.009719</v>
-      </c>
-      <c r="J270" s="5" t="n">
-        <v>0.008333999999999999</v>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K270" s="5" t="n">
-        <v>0.008911000000000001</v>
+        <v>0.191871</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>0.007214</v>
+        <v>0.041548</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
@@ -31737,12 +31765,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
+          <t>Transfer agent fees</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -31751,29 +31779,25 @@
         </is>
       </c>
       <c r="F271" s="5" t="n">
-        <v>0.008522999999999999</v>
+        <v>0.006381</v>
       </c>
       <c r="G271" s="5" t="n">
-        <v>0.00224</v>
+        <v>0.008324</v>
       </c>
       <c r="H271" s="5" t="n">
-        <v>0.00445</v>
+        <v>0.011285</v>
       </c>
       <c r="I271" s="5" t="n">
-        <v>0.030263</v>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009719</v>
+      </c>
+      <c r="J271" s="5" t="n">
+        <v>0.008333999999999999</v>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>0.008911000000000001</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>0.000844</v>
+        <v>0.007214</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
@@ -31824,37 +31848,43 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Travel and promotion</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E272" s="5" t="n">
-        <v>0.035096</v>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F272" s="5" t="n">
-        <v>0.123774</v>
+        <v>0.008522999999999999</v>
       </c>
       <c r="G272" s="5" t="n">
-        <v>0.150089</v>
+        <v>0.00224</v>
       </c>
       <c r="H272" s="5" t="n">
-        <v>0.251946</v>
+        <v>0.00445</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>0.211217</v>
-      </c>
-      <c r="J272" s="5" t="n">
-        <v>0.110049</v>
-      </c>
-      <c r="K272" s="5" t="n">
-        <v>0.481673</v>
+        <v>0.030263</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L272" s="5" t="n">
-        <v>0.227509</v>
+        <v>0.000844</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
@@ -31900,52 +31930,42 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium liability 5</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="n">
+        <v>0.035096</v>
+      </c>
+      <c r="F273" s="5" t="n">
+        <v>0.123774</v>
+      </c>
+      <c r="G273" s="5" t="n">
+        <v>0.150089</v>
+      </c>
+      <c r="H273" s="5" t="n">
+        <v>0.251946</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>0.211217</v>
+      </c>
+      <c r="J273" s="5" t="n">
+        <v>0.110049</v>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>0.481673</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>0.129507</v>
+        <v>0.227509</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
@@ -31996,7 +32016,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt</t>
+          <t>Amortization of flow-through premium liability 5</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -32025,16 +32045,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J274" s="5" t="n">
-        <v>0.00621</v>
-      </c>
-      <c r="K274" s="5" t="n">
-        <v>0.033854</v>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>0.129507</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
@@ -32085,7 +32107,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets 6</t>
+          <t>Gain on settlement of debt</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -32114,13 +32136,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J275" s="5" t="n">
+        <v>0.00621</v>
       </c>
       <c r="K275" s="5" t="n">
-        <v>-0.639686</v>
+        <v>0.033854</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -32176,7 +32196,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Other items total</t>
+          <t>Write-off of exploration and evaluation assets 6</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -32211,10 +32231,12 @@
         </is>
       </c>
       <c r="K276" s="5" t="n">
-        <v>-0.605832</v>
-      </c>
-      <c r="L276" s="5" t="n">
-        <v>0.129507</v>
+        <v>-0.639686</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
@@ -32265,14 +32287,10 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other items total</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -32304,10 +32322,10 @@
         </is>
       </c>
       <c r="K277" s="5" t="n">
-        <v>-1.087505</v>
+        <v>-0.605832</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>-0.09800200000000001</v>
+        <v>0.129507</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
@@ -32353,40 +32371,54 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Weighted average number of common</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F278" s="5" t="n">
-        <v>1.514696</v>
-      </c>
-      <c r="G278" s="5" t="n">
-        <v>1.014009</v>
-      </c>
-      <c r="H278" s="5" t="n">
-        <v>4.600927</v>
-      </c>
-      <c r="I278" s="5" t="n">
-        <v>22.921569</v>
-      </c>
-      <c r="J278" s="5" t="n">
-        <v>27.066702</v>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K278" s="5" t="n">
-        <v>37.120252</v>
+        <v>-1.087505</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>46.641745</v>
+        <v>-0.09800200000000001</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
@@ -32437,37 +32469,35 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Loss per common share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E279" s="5" t="n">
-        <v>0</v>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F279" s="5" t="n">
-        <v>-8e-08</v>
+        <v>1.514696</v>
       </c>
       <c r="G279" s="5" t="n">
-        <v>-1.5e-07</v>
+        <v>1.014009</v>
       </c>
       <c r="H279" s="5" t="n">
-        <v>-5e-08</v>
+        <v>4.600927</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>0</v>
+        <v>22.921569</v>
       </c>
       <c r="J279" s="5" t="n">
-        <v>0</v>
+        <v>27.066702</v>
       </c>
       <c r="K279" s="5" t="n">
-        <v>-3e-08</v>
+        <v>37.120252</v>
       </c>
       <c r="L279" s="5" t="n">
-        <v>0</v>
+        <v>46.641745</v>
       </c>
       <c r="M279" t="inlineStr">
         <is>
@@ -32513,50 +32543,42 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Office and administration 7</t>
+          <t>Loss per common share – basic and diluted $</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.024138</v>
+        <v>-8e-08</v>
       </c>
       <c r="G280" s="5" t="n">
-        <v>0.02339</v>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.5e-07</v>
+      </c>
+      <c r="H280" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="I280" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J280" s="5" t="n">
-        <v>0.03866</v>
+        <v>0</v>
       </c>
       <c r="K280" s="5" t="n">
-        <v>0.044971</v>
-      </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
@@ -32607,7 +32629,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Rent 7</t>
+          <t>Office and administration 7</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -32620,15 +32642,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F281" s="5" t="n">
+        <v>0.024138</v>
+      </c>
+      <c r="G281" s="5" t="n">
+        <v>0.02339</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -32641,10 +32659,10 @@
         </is>
       </c>
       <c r="J281" s="5" t="n">
-        <v>0.012</v>
+        <v>0.03866</v>
       </c>
       <c r="K281" s="5" t="n">
-        <v>0.012</v>
+        <v>0.044971</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -32700,10 +32718,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Stock-based compensation 6(e)</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Rent 7</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -32729,13 +32751,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J282" s="5" t="n">
+        <v>0.012</v>
       </c>
       <c r="K282" s="5" t="n">
-        <v>0.191871</v>
+        <v>0.012</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -32786,12 +32806,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>(639,686)                   –     assets</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>(639,686)                   –     assets total</t>
+          <t>Stock-based compensation 6(e)</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -32820,11 +32840,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J283" s="5" t="n">
-        <v>0.00621</v>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K283" s="5" t="n">
-        <v>-0.605832</v>
+        <v>0.191871</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -32880,14 +32902,10 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>(639,686)                   –     assets total</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -32914,10 +32932,10 @@
         </is>
       </c>
       <c r="J284" s="5" t="n">
-        <v>-0.103839</v>
+        <v>0.00621</v>
       </c>
       <c r="K284" s="5" t="n">
-        <v>-1.087505</v>
+        <v>-0.605832</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -32968,15 +32986,19 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>(639,686)                   –     assets</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Accretion of convertible debt 9 $</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -32997,18 +33019,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I285" s="5" t="n">
-        <v>0.007224</v>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J285" s="5" t="n">
+        <v>-0.103839</v>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>-1.087505</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -33064,14 +33084,10 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bank charges</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accretion of convertible debt 9 $</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -33082,17 +33098,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G286" s="5" t="n">
-        <v>0.000217</v>
-      </c>
-      <c r="H286" s="5" t="n">
-        <v>0.000469</v>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I286" s="5" t="n">
-        <v>0.000619</v>
-      </c>
-      <c r="J286" s="5" t="n">
-        <v>0.00026</v>
+        <v>0.007224</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -33153,12 +33175,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -33171,23 +33193,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G287" s="5" t="n">
+        <v>0.000217</v>
+      </c>
+      <c r="H287" s="5" t="n">
+        <v>0.000469</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>-7.9e-05</v>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000619</v>
+      </c>
+      <c r="J287" s="5" t="n">
+        <v>0.00026</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -33248,10 +33264,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Interest on convertible debt 9</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -33273,7 +33293,7 @@
         </is>
       </c>
       <c r="I288" s="5" t="n">
-        <v>0.016096</v>
+        <v>-7.9e-05</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -33339,7 +33359,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Stock-based compensation 7(d)</t>
+          <t>Interest on convertible debt 9</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -33364,7 +33384,7 @@
         </is>
       </c>
       <c r="I289" s="5" t="n">
-        <v>0.025563</v>
+        <v>0.016096</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -33425,12 +33445,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt 7(b)(iv)</t>
+          <t>Stock-based compensation 7(d)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -33454,13 +33474,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J290" s="5" t="n">
-        <v>0.00621</v>
+      <c r="I290" s="5" t="n">
+        <v>0.025563</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -33521,7 +33541,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Loss before taxes</t>
+          <t>Gain on settlement of debt 7(b)(iv)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -33545,11 +33565,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I291" s="5" t="n">
-        <v>-0.211217</v>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J291" s="5" t="n">
-        <v>-0.103839</v>
+        <v>0.00621</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -33610,7 +33632,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Deferred tax recovery 11</t>
+          <t>Loss before taxes</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -33635,12 +33657,10 @@
         </is>
       </c>
       <c r="I292" s="5" t="n">
-        <v>0.103768</v>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.211217</v>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>-0.103839</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -33701,14 +33721,10 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deferred tax recovery 11</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -33730,10 +33746,12 @@
         </is>
       </c>
       <c r="I293" s="5" t="n">
-        <v>-0.107449</v>
-      </c>
-      <c r="J293" s="5" t="n">
-        <v>-0.103839</v>
+        <v>0.103768</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -33787,13 +33805,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Accretion of convertible debt 7 $</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -33809,16 +33835,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H294" s="5" t="n">
-        <v>0.003421</v>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I294" s="5" t="n">
-        <v>0.007224</v>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.107449</v>
+      </c>
+      <c r="J294" s="5" t="n">
+        <v>-0.103839</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -33875,14 +33901,10 @@
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Bank charges</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accretion of convertible debt 7 $</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -33899,10 +33921,10 @@
         </is>
       </c>
       <c r="H295" s="5" t="n">
-        <v>0.000469</v>
+        <v>0.003421</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>0.000619</v>
+        <v>0.007224</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -33964,10 +33986,14 @@
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Due diligence</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -33984,12 +34010,10 @@
         </is>
       </c>
       <c r="H296" s="5" t="n">
-        <v>0.001602</v>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000469</v>
+      </c>
+      <c r="I296" s="5" t="n">
+        <v>0.000619</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -34051,14 +34075,10 @@
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Due diligence</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -34075,10 +34095,12 @@
         </is>
       </c>
       <c r="H297" s="5" t="n">
-        <v>-0.000595</v>
-      </c>
-      <c r="I297" s="5" t="n">
-        <v>-7.9e-05</v>
+        <v>0.001602</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -34140,10 +34162,14 @@
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Interest on convertible debt 7</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -34160,10 +34186,10 @@
         </is>
       </c>
       <c r="H298" s="5" t="n">
-        <v>0.005131</v>
+        <v>-0.000595</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>0.016096</v>
+        <v>-7.9e-05</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -34225,14 +34251,10 @@
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Office and administration 10</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Interest on convertible debt 7</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -34249,10 +34271,10 @@
         </is>
       </c>
       <c r="H299" s="5" t="n">
-        <v>0.02373</v>
+        <v>0.005131</v>
       </c>
       <c r="I299" s="5" t="n">
-        <v>0.049035</v>
+        <v>0.016096</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -34314,12 +34336,12 @@
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and administration 10</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -34338,10 +34360,10 @@
         </is>
       </c>
       <c r="H300" s="5" t="n">
-        <v>0.138562</v>
+        <v>0.02373</v>
       </c>
       <c r="I300" s="5" t="n">
-        <v>0.053465</v>
+        <v>0.049035</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -34403,12 +34425,12 @@
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -34427,10 +34449,10 @@
         </is>
       </c>
       <c r="H301" s="5" t="n">
-        <v>0.012581</v>
+        <v>0.138562</v>
       </c>
       <c r="I301" s="5" t="n">
-        <v>0.007312</v>
+        <v>0.053465</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -34492,7 +34514,7 @@
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Rent 10</t>
+          <t>Regulatory fees</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -34516,10 +34538,10 @@
         </is>
       </c>
       <c r="H302" s="5" t="n">
-        <v>0.001</v>
+        <v>0.012581</v>
       </c>
       <c r="I302" s="5" t="n">
-        <v>0.012</v>
+        <v>0.007312</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -34581,10 +34603,14 @@
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Stock-based compensation 9</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Rent 10</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -34601,10 +34627,10 @@
         </is>
       </c>
       <c r="H303" s="5" t="n">
-        <v>0.049715</v>
+        <v>0.001</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>0.025563</v>
+        <v>0.012</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -34666,14 +34692,10 @@
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Stock-based compensation 9</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -34690,10 +34712,10 @@
         </is>
       </c>
       <c r="H304" s="5" t="n">
-        <v>0.011285</v>
+        <v>0.049715</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>0.009719</v>
+        <v>0.025563</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -34755,12 +34777,12 @@
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
+          <t>Transfer agent fees</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -34779,10 +34801,10 @@
         </is>
       </c>
       <c r="H305" s="5" t="n">
-        <v>0.00445</v>
+        <v>0.011285</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>0.030263</v>
+        <v>0.009719</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -34844,10 +34866,14 @@
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Loss before taxes</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Travel and promotion</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -34864,10 +34890,10 @@
         </is>
       </c>
       <c r="H306" s="5" t="n">
-        <v>-0.251351</v>
+        <v>0.00445</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>-0.211217</v>
+        <v>0.030263</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -34929,7 +34955,7 @@
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Deferred tax recovery 12</t>
+          <t>Loss before taxes</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -34948,13 +34974,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H307" s="5" t="n">
+        <v>-0.251351</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>0.103768</v>
+        <v>-0.211217</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -35016,14 +35040,10 @@
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deferred tax recovery 12</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -35039,11 +35059,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H308" s="5" t="n">
-        <v>-0.251351</v>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I308" s="5" t="n">
-        <v>-0.107449</v>
+        <v>0.103768</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -35102,17 +35124,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Accretion of convertible debt 7 $</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -35129,12 +35151,10 @@
         </is>
       </c>
       <c r="H309" s="5" t="n">
-        <v>0.003421</v>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.251351</v>
+      </c>
+      <c r="I309" s="5" t="n">
+        <v>-0.107449</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -35200,7 +35220,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Corporate financing fee</t>
+          <t>Accretion of convertible debt 7 $</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -35214,13 +35234,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G310" s="5" t="n">
-        <v>0.0112</v>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H310" s="5" t="n">
+        <v>0.003421</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -35291,7 +35311,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Due diligence</t>
+          <t>Corporate financing fee</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -35306,10 +35326,12 @@
         </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>0.001646</v>
-      </c>
-      <c r="H311" s="5" t="n">
-        <v>0.001602</v>
+        <v>0.0112</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -35380,7 +35402,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Interest on convertible debt 7</t>
+          <t>Due diligence</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -35394,13 +35416,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G312" s="5" t="n">
+        <v>0.001646</v>
       </c>
       <c r="H312" s="5" t="n">
-        <v>0.005131</v>
+        <v>0.001602</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -35471,14 +35491,10 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Office and administration 11</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Interest on convertible debt 7</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -35489,11 +35505,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G313" s="5" t="n">
-        <v>0.023173</v>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H313" s="5" t="n">
-        <v>0.02473</v>
+        <v>0.005131</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -35564,10 +35582,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Share-based compensation 9</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>Office and administration 11</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -35579,10 +35601,10 @@
         </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>0.001511</v>
+        <v>0.023173</v>
       </c>
       <c r="H314" s="5" t="n">
-        <v>0.049715</v>
+        <v>0.02473</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -35648,32 +35670,30 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Share-based compensation 9</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F315" s="5" t="n">
-        <v>0.001687</v>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>0.001638</v>
+        <v>0.001511</v>
       </c>
       <c r="H315" s="5" t="n">
-        <v>0.000595</v>
+        <v>0.049715</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -35744,21 +35764,27 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" s="5" t="n">
-        <v>-0.035096</v>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F316" s="5" t="n">
-        <v>-0.122087</v>
+        <v>0.001687</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>-0.148451</v>
+        <v>0.001638</v>
       </c>
       <c r="H316" s="5" t="n">
-        <v>-0.251351</v>
+        <v>0.000595</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -35824,36 +35850,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Consulting 1 $</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" s="5" t="n">
+        <v>-0.035096</v>
+      </c>
+      <c r="F317" s="5" t="n">
+        <v>-0.122087</v>
       </c>
       <c r="G317" s="5" t="n">
-        <v>0.0224</v>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.148451</v>
+      </c>
+      <c r="H317" s="5" t="n">
+        <v>-0.251351</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -35924,10 +35940,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Due diligence 1</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>Consulting 1 $</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -35939,7 +35959,7 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>0.012846</v>
+        <v>0.0224</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -36015,7 +36035,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Share-based compensation 6</t>
+          <t>Due diligence 1</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -36024,11 +36044,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F319" s="5" t="n">
-        <v>0.034376</v>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G319" s="5" t="n">
-        <v>0.001511</v>
+        <v>0.012846</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -36099,25 +36121,25 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>For the period from</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>Share-based compensation 6</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" s="5" t="n">
-        <v>0.002011</v>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F320" s="5" t="n">
-        <v>9e-06</v>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.034376</v>
+      </c>
+      <c r="G320" s="5" t="n">
+        <v>0.001511</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -36193,7 +36215,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Note May 31, 2012 May</t>
+          <t>February</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -36201,7 +36223,7 @@
         <v>0.002011</v>
       </c>
       <c r="F321" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>9e-06</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -36277,24 +36299,20 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>For the period from</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Bank charges $</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Note May 31, 2012 May</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
       <c r="E322" s="5" t="n">
-        <v>4.3e-05</v>
+        <v>0.002011</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.000137</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -36375,7 +36393,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Office and administration 9</t>
+          <t>Bank charges $</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -36384,10 +36402,10 @@
         </is>
       </c>
       <c r="E323" s="5" t="n">
-        <v>0.003624</v>
+        <v>4.3e-05</v>
       </c>
       <c r="F323" s="5" t="n">
-        <v>0.024001</v>
+        <v>0.000137</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -36468,79 +36486,172 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
+          <t>Office and administration 9</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="n">
+        <v>0.003624</v>
+      </c>
+      <c r="F324" s="5" t="n">
+        <v>0.024001</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
           <t>Share-based compensation 7,9</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F324" s="5" t="n">
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F325" s="5" t="n">
         <v>0.034376</v>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S324" t="inlineStr">
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
